--- a/output/yearly_surface_area_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_76_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497652125712</v>
+        <v>10.84497642522887</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907260062222</v>
+        <v>37.78907226601399</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.420809912223387</v>
+        <v>5.769731257858504</v>
       </c>
       <c r="C2" t="n">
-        <v>11.93216159741573</v>
+        <v>14.63589477491145</v>
       </c>
       <c r="D2" t="n">
-        <v>24.39544870282899</v>
+        <v>25.73062558060465</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.80828146023139</v>
+        <v>19.38951715887451</v>
       </c>
       <c r="C3" t="n">
-        <v>26.89006961932013</v>
+        <v>19.64968030049991</v>
       </c>
       <c r="D3" t="n">
-        <v>83.88543258936872</v>
+        <v>71.47614160768903</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.22212132753381</v>
+        <v>40.86622993697772</v>
       </c>
       <c r="C4" t="n">
-        <v>67.69346770322606</v>
+        <v>55.21152739143212</v>
       </c>
       <c r="D4" t="n">
-        <v>99.97038697574845</v>
+        <v>83.25122357242527</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.23907308041327</v>
+        <v>46.4612101034803</v>
       </c>
       <c r="C5" t="n">
-        <v>122.7184630308513</v>
+        <v>117.4170254279185</v>
       </c>
       <c r="D5" t="n">
-        <v>70.41585408710249</v>
+        <v>61.21196935978864</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.30070220160257</v>
+        <v>37.75605320992383</v>
       </c>
       <c r="C6" t="n">
-        <v>170.4255109710208</v>
+        <v>141.7663319886479</v>
       </c>
       <c r="D6" t="n">
-        <v>46.81267578160067</v>
+        <v>44.63908636439822</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C7" t="n">
-        <v>166.0655694164607</v>
+        <v>118.1562814492164</v>
       </c>
       <c r="D7" t="n">
-        <v>39.1059563032632</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>111.1534750748239</v>
+        <v>76.18853058807372</v>
       </c>
       <c r="D8" t="n">
-        <v>35.13184159647211</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>57.57655761096267</v>
+        <v>41.82343394861835</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.632563420952075</v>
+        <v>7.687134782622017</v>
       </c>
       <c r="C21" t="n">
-        <v>91.59076105142489</v>
+        <v>94.1674010871197</v>
       </c>
       <c r="D21" t="n">
-        <v>7.632563420952075</v>
+        <v>8.648026630449769</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.922482989093507</v>
+        <v>6.276313073249859</v>
       </c>
       <c r="C2" t="n">
-        <v>10.97986632429633</v>
+        <v>16.19196488614264</v>
       </c>
       <c r="D2" t="n">
-        <v>31.44537896702534</v>
+        <v>29.47501132460199</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.06844460185679</v>
+        <v>19.20789383358884</v>
       </c>
       <c r="C3" t="n">
-        <v>36.11358930071892</v>
+        <v>38.70049450140927</v>
       </c>
       <c r="D3" t="n">
-        <v>83.25711405865076</v>
+        <v>74.44592841303563</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.88654353913065</v>
+        <v>38.49236398810894</v>
       </c>
       <c r="C4" t="n">
-        <v>66.63416193034375</v>
+        <v>52.07189823325082</v>
       </c>
       <c r="D4" t="n">
-        <v>115.0686849193602</v>
+        <v>97.45613110517236</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.06159773012285</v>
+        <v>52.96528864411543</v>
       </c>
       <c r="C5" t="n">
-        <v>123.4547738090364</v>
+        <v>108.6549271675158</v>
       </c>
       <c r="D5" t="n">
-        <v>85.14206965080464</v>
+        <v>73.95014582239101</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.62650357069227</v>
+        <v>49.42903341341842</v>
       </c>
       <c r="C6" t="n">
-        <v>180.2066633484318</v>
+        <v>163.2607162254276</v>
       </c>
       <c r="D6" t="n">
-        <v>55.58753676215866</v>
+        <v>52.56866257159972</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.91956310817654</v>
+        <v>34.2551408965797</v>
       </c>
       <c r="C7" t="n">
-        <v>202.8359479313208</v>
+        <v>157.8012172421111</v>
       </c>
       <c r="D7" t="n">
-        <v>43.17824578047897</v>
+        <v>42.04040019125691</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.60902773399829</v>
+        <v>19.69385894719101</v>
       </c>
       <c r="C8" t="n">
-        <v>158.3019085712769</v>
+        <v>114.2410716046801</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>92.2999921624681</v>
+        <v>65.78593191387449</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>48.25780840225197</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
         <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.50740899884213</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.799906682315055</v>
+        <v>7.866423369533669</v>
       </c>
       <c r="C21" t="n">
-        <v>99.44881019951696</v>
+        <v>102.2635038039377</v>
       </c>
       <c r="D21" t="n">
-        <v>8.774895017604438</v>
+        <v>9.833029211917086</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.569274799742908</v>
+        <v>8.431249284071608</v>
       </c>
       <c r="C2" t="n">
-        <v>13.77588378599124</v>
+        <v>15.87584212537517</v>
       </c>
       <c r="D2" t="n">
-        <v>25.94268308472196</v>
+        <v>40.81419730865264</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.68203691701105</v>
+        <v>19.68404147014855</v>
       </c>
       <c r="C3" t="n">
-        <v>38.64649837767569</v>
+        <v>49.57825906446393</v>
       </c>
       <c r="D3" t="n">
-        <v>87.60134764994289</v>
+        <v>78.43182409227768</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.58474608329938</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C4" t="n">
-        <v>76.49974461031996</v>
+        <v>71.45847014901258</v>
       </c>
       <c r="D4" t="n">
-        <v>124.0919280690926</v>
+        <v>107.3855273859246</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.938879267092</v>
+        <v>54.51154127830416</v>
       </c>
       <c r="C5" t="n">
-        <v>121.5403657857552</v>
+        <v>102.7889846346411</v>
       </c>
       <c r="D5" t="n">
-        <v>100.0155473701438</v>
+        <v>88.03822537833273</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.2956956520901</v>
+        <v>58.20389439397641</v>
       </c>
       <c r="C6" t="n">
-        <v>185.4393786120673</v>
+        <v>166.2393387601124</v>
       </c>
       <c r="D6" t="n">
-        <v>66.1334706011779</v>
+        <v>60.57874209054944</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.04606969330414</v>
+        <v>44.25620475974196</v>
       </c>
       <c r="C7" t="n">
-        <v>227.6888910643287</v>
+        <v>190.3795330598372</v>
       </c>
       <c r="D7" t="n">
-        <v>47.31042186765379</v>
+        <v>46.53189593818607</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.70077223884975</v>
+        <v>26.8704346652352</v>
       </c>
       <c r="C8" t="n">
-        <v>201.695157098986</v>
+        <v>155.5481062608646</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.86874890726719</v>
+        <v>14.19999879422586</v>
       </c>
       <c r="C9" t="n">
-        <v>133.0140512052876</v>
+        <v>97.07030425740334</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>71.74612222635692</v>
+        <v>55.51783267515713</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>41.5809422656694</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.32797015314322</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.950847109337719</v>
+        <v>8.029126403115406</v>
       </c>
       <c r="C21" t="n">
-        <v>106.342580087392</v>
+        <v>110.4004880428368</v>
       </c>
       <c r="D21" t="n">
-        <v>9.938558886672149</v>
+        <v>11.04004880428368</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.761296439147783</v>
+        <v>7.625234418884976</v>
       </c>
       <c r="C2" t="n">
-        <v>9.697703822549993</v>
+        <v>10.92194320974577</v>
       </c>
       <c r="D2" t="n">
-        <v>21.59452250261284</v>
+        <v>33.40396563699773</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.71563732313369</v>
+        <v>24.58296251434013</v>
       </c>
       <c r="C3" t="n">
-        <v>56.4210405630642</v>
+        <v>67.82894888641214</v>
       </c>
       <c r="D3" t="n">
-        <v>95.00863407848507</v>
+        <v>84.2143180702914</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.66735175917635</v>
+        <v>26.18910175848792</v>
       </c>
       <c r="C4" t="n">
-        <v>101.0552181889412</v>
+        <v>90.41110957949726</v>
       </c>
       <c r="D4" t="n">
-        <v>116.2556178937945</v>
+        <v>101.7316423571672</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.62990647769474</v>
+        <v>32.79037332184348</v>
       </c>
       <c r="C5" t="n">
-        <v>110.7902284242526</v>
+        <v>99.32832397717107</v>
       </c>
       <c r="D5" t="n">
-        <v>65.43348448804993</v>
+        <v>59.86206626644928</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.23149683621978</v>
+        <v>27.45162930614931</v>
       </c>
       <c r="C6" t="n">
-        <v>149.9374181310941</v>
+        <v>125.3839080478814</v>
       </c>
       <c r="D6" t="n">
-        <v>31.15478164656829</v>
+        <v>30.63151012020474</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>17.78632315783946</v>
       </c>
       <c r="C7" t="n">
-        <v>141.8114923830433</v>
+        <v>109.3529497852352</v>
       </c>
       <c r="D7" t="n">
-        <v>27.78738702100172</v>
+        <v>28.086820070797</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>98.05205196165018</v>
+        <v>71.5154115158589</v>
       </c>
       <c r="D8" t="n">
-        <v>26.45319189093031</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>54.69218285588555</v>
+        <v>42.3781214015178</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.967242472861361</v>
+        <v>4.469897297435728</v>
       </c>
       <c r="C2" t="n">
-        <v>4.447317100238051</v>
+        <v>5.088398351111218</v>
       </c>
       <c r="D2" t="n">
-        <v>16.13895051011331</v>
+        <v>24.39741219823749</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.53816197284327</v>
+        <v>26.02122290106171</v>
       </c>
       <c r="C3" t="n">
-        <v>48.25289966373073</v>
+        <v>56.13633372883262</v>
       </c>
       <c r="D3" t="n">
-        <v>91.34671514164448</v>
+        <v>91.43016369650546</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.44886398948582</v>
+        <v>35.46759931132452</v>
       </c>
       <c r="C4" t="n">
-        <v>122.9815714155894</v>
+        <v>131.5964075203552</v>
       </c>
       <c r="D4" t="n">
-        <v>133.7788326668959</v>
+        <v>116.4853468565883</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.30516897176729</v>
+        <v>36.64373306101221</v>
       </c>
       <c r="C5" t="n">
-        <v>144.8077863764046</v>
+        <v>132.0696099138022</v>
       </c>
       <c r="D5" t="n">
-        <v>82.90859362364314</v>
+        <v>76.13453446434016</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.13590745600934</v>
+        <v>33.12711278440013</v>
       </c>
       <c r="C6" t="n">
-        <v>169.4997228859161</v>
+        <v>144.4229412763398</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>37.63529824230149</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.21119892960008</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>172.7728697318749</v>
+        <v>139.356141374722</v>
       </c>
       <c r="D7" t="n">
-        <v>30.42239785920016</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>128.1769802664635</v>
+        <v>94.29686699290613</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>56.91093266748334</v>
+        <v>47.59218345877262</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.120395114723864</v>
+        <v>4.16751900452771</v>
       </c>
       <c r="C2" t="n">
-        <v>9.689849840916018</v>
+        <v>13.03760951239764</v>
       </c>
       <c r="D2" t="n">
-        <v>16.35984374356885</v>
+        <v>22.21204180858409</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.17567608579795</v>
+        <v>20.80814259151115</v>
       </c>
       <c r="C3" t="n">
-        <v>32.33876937788994</v>
+        <v>37.3211389769425</v>
       </c>
       <c r="D3" t="n">
-        <v>84.63646958311753</v>
+        <v>89.43721585688444</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.396291581813</v>
+        <v>41.78514578815274</v>
       </c>
       <c r="C4" t="n">
-        <v>121.5776721985165</v>
+        <v>135.744291570798</v>
       </c>
       <c r="D4" t="n">
-        <v>144.3591276755637</v>
+        <v>132.7195268940135</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.28124717396688</v>
+        <v>44.08047192068179</v>
       </c>
       <c r="C5" t="n">
-        <v>184.5440247057942</v>
+        <v>185.0594422505238</v>
       </c>
       <c r="D5" t="n">
-        <v>107.1577619185394</v>
+        <v>96.53034302006766</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.00635781677777</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="C6" t="n">
-        <v>196.6293389450724</v>
+        <v>176.3022527286422</v>
       </c>
       <c r="D6" t="n">
-        <v>51.80388110999145</v>
+        <v>49.67054334866313</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.21793229480956</v>
+        <v>25.63146906247572</v>
       </c>
       <c r="C7" t="n">
-        <v>207.0280106284546</v>
+        <v>172.4734366820796</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>172.4047143427823</v>
+        <v>134.268724771315</v>
       </c>
       <c r="D8" t="n">
-        <v>28.70630287217673</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>97.40311672914301</v>
+        <v>76.21405602838412</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>47.11898106532567</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.474004214701962</v>
+        <v>2.509347132054847</v>
       </c>
       <c r="C2" t="n">
-        <v>4.756567627075796</v>
+        <v>6.304783756673016</v>
       </c>
       <c r="D2" t="n">
-        <v>11.54633474964674</v>
+        <v>15.50375974546563</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.47020039707199</v>
+        <v>20.2681813541754</v>
       </c>
       <c r="C3" t="n">
-        <v>36.2264902867073</v>
+        <v>44.860961345558</v>
       </c>
       <c r="D3" t="n">
-        <v>82.5993430968054</v>
+        <v>89.6777440444249</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.44658169890783</v>
+        <v>45.57567367424968</v>
       </c>
       <c r="C4" t="n">
-        <v>120.3652137837717</v>
+        <v>134.9912910816407</v>
       </c>
       <c r="D4" t="n">
-        <v>153.7780151501076</v>
+        <v>144.1549241530804</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.7538687303371</v>
+        <v>45.08676331753477</v>
       </c>
       <c r="C5" t="n">
-        <v>223.8875639534852</v>
+        <v>228.0354480039279</v>
       </c>
       <c r="D5" t="n">
-        <v>109.8575681052181</v>
+        <v>102.34719816773</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.60634453279281</v>
+        <v>31.87931145230244</v>
       </c>
       <c r="C6" t="n">
-        <v>233.7011140051363</v>
+        <v>210.9589284362589</v>
       </c>
       <c r="D6" t="n">
-        <v>50.27431818677493</v>
+        <v>48.90576188705487</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.066619975168541</v>
+        <v>7.845145904636261</v>
       </c>
       <c r="C7" t="n">
-        <v>217.9273736410027</v>
+        <v>177.6236851385584</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>120.7500588838364</v>
+        <v>95.63204387068178</v>
       </c>
       <c r="D8" t="n">
-        <v>30.70906818884022</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>35.94374694788421</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.01350778814797</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.53673825678252</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.173990327829938</v>
+        <v>3.209333245182823</v>
       </c>
       <c r="C2" t="n">
-        <v>5.929756133650734</v>
+        <v>5.790347959647687</v>
       </c>
       <c r="D2" t="n">
-        <v>15.09535270049896</v>
+        <v>11.87816547368216</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.233959053247</v>
+        <v>14.72130682518092</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5625667967292</v>
+        <v>34.92567457858028</v>
       </c>
       <c r="D3" t="n">
-        <v>73.9943244690821</v>
+        <v>82.23609644623407</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.68081848959532</v>
+        <v>42.67853619901734</v>
       </c>
       <c r="C4" t="n">
-        <v>107.1940865835965</v>
+        <v>123.9004872667645</v>
       </c>
       <c r="D4" t="n">
-        <v>158.4619334470692</v>
+        <v>153.433421705917</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.65064635267094</v>
+        <v>54.53608497091033</v>
       </c>
       <c r="C5" t="n">
-        <v>222.4149423971149</v>
+        <v>239.1046533693107</v>
       </c>
       <c r="D5" t="n">
-        <v>134.3276296335698</v>
+        <v>124.4119778206771</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.21390749300134</v>
+        <v>42.2642386678252</v>
       </c>
       <c r="C6" t="n">
-        <v>290.013180573029</v>
+        <v>276.8911407580662</v>
       </c>
       <c r="D6" t="n">
-        <v>65.81145735418494</v>
+        <v>64.72466264558373</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.31289978021425</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>268.2920126165683</v>
+        <v>233.0786859606437</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>38.32743037379547</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>185.756483120539</v>
+        <v>149.5398103108741</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>74.77186865084555</v>
+        <v>62.23593221531803</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.008655802888974</v>
+        <v>2.291399141712055</v>
       </c>
       <c r="C2" t="n">
-        <v>4.066398990990288</v>
+        <v>3.183807804872406</v>
       </c>
       <c r="D2" t="n">
-        <v>10.91801621892878</v>
+        <v>8.814130888727863</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.30620747273377</v>
+        <v>13.26341148437441</v>
       </c>
       <c r="C3" t="n">
-        <v>25.83469083725482</v>
+        <v>30.07584091960103</v>
       </c>
       <c r="D3" t="n">
-        <v>70.24895697738052</v>
+        <v>75.33441008537899</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.15379989886403</v>
+        <v>37.85422798034851</v>
       </c>
       <c r="C4" t="n">
-        <v>94.40584098807754</v>
+        <v>112.1715474441278</v>
       </c>
       <c r="D4" t="n">
-        <v>159.3936120183994</v>
+        <v>157.7727465586879</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.28311285838414</v>
+        <v>59.51845456996289</v>
       </c>
       <c r="C5" t="n">
-        <v>220.8441460703201</v>
+        <v>240.7245370813179</v>
       </c>
       <c r="D5" t="n">
-        <v>150.7964473723101</v>
+        <v>141.0280577150543</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.40637110076273</v>
+        <v>49.1875234781737</v>
       </c>
       <c r="C6" t="n">
-        <v>323.2207966691774</v>
+        <v>321.8522403694574</v>
       </c>
       <c r="D6" t="n">
-        <v>78.16871570753956</v>
+        <v>75.91462297858888</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.81573453123786</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>319.1357444718064</v>
+        <v>289.2523261022378</v>
       </c>
       <c r="D7" t="n">
-        <v>42.93869934064274</v>
+        <v>42.57937968088841</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>233.4890565010189</v>
+        <v>189.4282195344221</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>78.76561831172157</v>
+        <v>68.78124415953151</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.85664913964673</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.5087662949781</v>
+        <v>4.116468123906875</v>
       </c>
       <c r="C2" t="n">
-        <v>8.011061266653973</v>
+        <v>4.411974182885166</v>
       </c>
       <c r="D2" t="n">
-        <v>16.87820653141116</v>
+        <v>15.38889526406875</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.729119749085891</v>
+        <v>10.66178006812036</v>
       </c>
       <c r="C3" t="n">
-        <v>21.46100481483528</v>
+        <v>22.09423208407447</v>
       </c>
       <c r="D3" t="n">
-        <v>64.10812508731672</v>
+        <v>67.13190801639689</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.58023825540564</v>
+        <v>31.91956310817654</v>
       </c>
       <c r="C4" t="n">
-        <v>80.81354402278045</v>
+        <v>96.12880820903068</v>
       </c>
       <c r="D4" t="n">
-        <v>157.6706447974462</v>
+        <v>158.0918145625681</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.52854978444584</v>
+        <v>58.88031856220246</v>
       </c>
       <c r="C5" t="n">
-        <v>201.1601046001715</v>
+        <v>226.0964962880405</v>
       </c>
       <c r="D5" t="n">
-        <v>164.197303535279</v>
+        <v>155.6315548157257</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.81267578160067</v>
+        <v>59.77370897306707</v>
       </c>
       <c r="C6" t="n">
-        <v>334.8132735609238</v>
+        <v>345.8824789263066</v>
       </c>
       <c r="D6" t="n">
-        <v>98.25429198872504</v>
+        <v>94.30962971306137</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.17611805415445</v>
+        <v>28.38625312059227</v>
       </c>
       <c r="C7" t="n">
-        <v>379.202014260739</v>
+        <v>356.0258962065845</v>
       </c>
       <c r="D7" t="n">
-        <v>51.08327829507428</v>
+        <v>50.36463897556562</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>301.6665258224386</v>
+        <v>262.3622564829176</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>149.8765497734308</v>
+        <v>125.0265518835355</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>50.82016991033614</v>
+        <v>47.11898106532567</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>10.75504610002381</v>
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.630903920932204</v>
+        <v>4.640721397974672</v>
       </c>
       <c r="C2" t="n">
-        <v>15.2514505854742</v>
+        <v>6.899722865446583</v>
       </c>
       <c r="D2" t="n">
-        <v>13.08571514990573</v>
+        <v>7.834346679889546</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.559416264971435</v>
+        <v>3.00709321810798</v>
       </c>
       <c r="C2" t="n">
-        <v>4.741841411512095</v>
+        <v>2.611448893296516</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5565531373167</v>
+        <v>11.4491417269263</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.16523671394973</v>
+        <v>14.74585051778709</v>
       </c>
       <c r="C3" t="n">
-        <v>27.58220175081414</v>
+        <v>24.45533531278805</v>
       </c>
       <c r="D3" t="n">
-        <v>70.92636289331082</v>
+        <v>73.42491080061895</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.7483791547391</v>
+        <v>44.32492709903924</v>
       </c>
       <c r="C4" t="n">
-        <v>116.2300924534841</v>
+        <v>135.2720709250553</v>
       </c>
       <c r="D4" t="n">
-        <v>159.73820546259</v>
+        <v>159.0490185742088</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.77716863333176</v>
+        <v>34.21390749300135</v>
       </c>
       <c r="C5" t="n">
-        <v>291.5790681613028</v>
+        <v>310.5513425458723</v>
       </c>
       <c r="D5" t="n">
-        <v>148.1457285708437</v>
+        <v>140.7826207889926</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.36984114706057</v>
+        <v>17.5899736169901</v>
       </c>
       <c r="C6" t="n">
-        <v>305.5503197404391</v>
+        <v>295.4874057719093</v>
       </c>
       <c r="D6" t="n">
-        <v>76.75990775194538</v>
+        <v>74.46556336712058</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.311835917051991</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>212.1183724749743</v>
+        <v>184.5106452838498</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>110.402438081075</v>
+        <v>92.12720456652069</v>
       </c>
       <c r="D8" t="n">
-        <v>23.86628669023996</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.71718421238145</v>
+        <v>35.94374694788421</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64124548178919</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
         <v>8.845546815263763</v>
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.653304191680633</v>
+        <v>5.817836895366598</v>
       </c>
       <c r="C2" t="n">
-        <v>8.201520321277853</v>
+        <v>6.282203559475339</v>
       </c>
       <c r="D2" t="n">
-        <v>18.87115437103219</v>
+        <v>18.09164669386022</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.842020735074275</v>
+        <v>9.86165568915921</v>
       </c>
       <c r="C3" t="n">
-        <v>38.43051388274139</v>
+        <v>17.38675184221101</v>
       </c>
       <c r="D3" t="n">
-        <v>14.1273494641116</v>
+        <v>9.714393533522189</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3963457469178</v>
+        <v>13.39867628738219</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13381008680494</v>
+        <v>70.14601115158909</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576040676107976</v>
+        <v>1.576314857339081</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.39822971502571</v>
+        <v>4.297109701488289</v>
       </c>
       <c r="C2" t="n">
-        <v>6.601271563355553</v>
+        <v>7.961973881441631</v>
       </c>
       <c r="D2" t="n">
-        <v>20.07085006562179</v>
+        <v>17.64691498383642</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.68127615348505</v>
+        <v>15.98285262513807</v>
       </c>
       <c r="C3" t="n">
-        <v>34.395530818287</v>
+        <v>21.83406894244906</v>
       </c>
       <c r="D3" t="n">
-        <v>26.56118413839745</v>
+        <v>22.5605622435917</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.55026174046372</v>
+        <v>11.56302446061893</v>
       </c>
       <c r="C4" t="n">
-        <v>59.09139431861551</v>
+        <v>27.01867856857647</v>
       </c>
       <c r="D4" t="n">
-        <v>22.47515019332223</v>
+        <v>20.16509784522949</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.117048960983624</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4980,7 +4980,7 @@
         <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
         <v>44.74806035956962</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43422217533645</v>
+        <v>15.44219851624283</v>
       </c>
       <c r="C21" t="n">
-        <v>86.10671318871916</v>
+        <v>86.15121277482841</v>
       </c>
       <c r="D21" t="n">
-        <v>3.24930993164978</v>
+        <v>3.250989161314279</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.677046063031804</v>
+        <v>4.603414985213294</v>
       </c>
       <c r="C2" t="n">
-        <v>11.24690169985146</v>
+        <v>7.598727230870312</v>
       </c>
       <c r="D2" t="n">
-        <v>18.09066494615598</v>
+        <v>16.80850244440964</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.27737693641212</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="C3" t="n">
-        <v>29.18245050873644</v>
+        <v>27.38094347144354</v>
       </c>
       <c r="D3" t="n">
-        <v>36.45229225868407</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.00667661194726</v>
+        <v>22.46238747316702</v>
       </c>
       <c r="C4" t="n">
-        <v>74.7512519490564</v>
+        <v>43.30390948662256</v>
       </c>
       <c r="D4" t="n">
-        <v>30.73263013374215</v>
+        <v>26.94210224764522</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.45561305022853</v>
+        <v>10.60287520586555</v>
       </c>
       <c r="C5" t="n">
-        <v>63.51907646476864</v>
+        <v>30.75324683553134</v>
       </c>
       <c r="D5" t="n">
-        <v>31.02322745419922</v>
+        <v>29.69786805346602</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>49.39663573917827</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.71830861110582</v>
+        <v>16.73697069604042</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1457670971902</v>
+        <v>102.0955212458466</v>
       </c>
       <c r="D21" t="n">
-        <v>4.179577152776456</v>
+        <v>5.021091208812125</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.6014514898048</v>
+        <v>6.413757751844412</v>
       </c>
       <c r="C2" t="n">
-        <v>6.586545347791851</v>
+        <v>9.325621442640452</v>
       </c>
       <c r="D2" t="n">
-        <v>36.43952953852886</v>
+        <v>17.50554331442488</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.23319828972101</v>
+        <v>15.59015354343935</v>
       </c>
       <c r="C3" t="n">
-        <v>37.34568266954867</v>
+        <v>28.58358440914589</v>
       </c>
       <c r="D3" t="n">
-        <v>42.092432819582</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.6695772964921</v>
+        <v>26.52093248252334</v>
       </c>
       <c r="C4" t="n">
-        <v>73.78128521726053</v>
+        <v>56.9727827728509</v>
       </c>
       <c r="D4" t="n">
-        <v>41.47884050442774</v>
+        <v>36.11849803924015</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.80109043113217</v>
+        <v>22.0402359603409</v>
       </c>
       <c r="C5" t="n">
-        <v>103.0098778680966</v>
+        <v>57.82493978013714</v>
       </c>
       <c r="D5" t="n">
-        <v>34.92567457858028</v>
+        <v>32.32404316232624</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.02266231265569</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>56.99634471775284</v>
+        <v>31.47679489356124</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28806265463436</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.02915100703044</v>
+        <v>18.06473401811307</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7602160455304</v>
+        <v>117.8508838324519</v>
       </c>
       <c r="D21" t="n">
-        <v>6.009717002343478</v>
+        <v>6.881803435471645</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.554728510628453</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="C2" t="n">
-        <v>5.85416156042373</v>
+        <v>6.13101441302133</v>
       </c>
       <c r="D2" t="n">
-        <v>33.46188875154829</v>
+        <v>32.63525718457247</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.06844460185679</v>
+        <v>17.0824100538945</v>
       </c>
       <c r="C3" t="n">
-        <v>28.86338250485623</v>
+        <v>30.96923133046564</v>
       </c>
       <c r="D3" t="n">
-        <v>55.76817833974007</v>
+        <v>39.74605580643212</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.26269177857742</v>
+        <v>20.66284393128262</v>
       </c>
       <c r="C4" t="n">
-        <v>70.41192709628548</v>
+        <v>54.06288257746336</v>
       </c>
       <c r="D4" t="n">
-        <v>44.89924950602363</v>
+        <v>40.18980576875168</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.41406085148068</v>
+        <v>18.99681807717579</v>
       </c>
       <c r="C5" t="n">
-        <v>88.38183707481912</v>
+        <v>62.26734814185396</v>
       </c>
       <c r="D5" t="n">
-        <v>33.69848994827177</v>
+        <v>30.31146036862028</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.98870205363455</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>74.82782826998766</v>
+        <v>42.7070068824405</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>30.99377502307181</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>32.39865598784899</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.52187317249857</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.038345648198515</v>
+        <v>7.061011466902607</v>
       </c>
       <c r="C21" t="n">
-        <v>65.98449045186108</v>
+        <v>66.19698250221194</v>
       </c>
       <c r="D21" t="n">
-        <v>4.398966030124072</v>
+        <v>5.295758600176955</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.563163329339175</v>
+        <v>6.373506095970292</v>
       </c>
       <c r="C2" t="n">
-        <v>7.898160280665589</v>
+        <v>3.388993075059989</v>
       </c>
       <c r="D2" t="n">
-        <v>31.59754986118359</v>
+        <v>26.07816426790802</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.20021977840412</v>
+        <v>23.39504779220149</v>
       </c>
       <c r="C3" t="n">
-        <v>25.08856258202724</v>
+        <v>26.44828315240908</v>
       </c>
       <c r="D3" t="n">
-        <v>70.40112787153878</v>
+        <v>57.55495916146926</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.12979598560561</v>
+        <v>28.67783218875358</v>
       </c>
       <c r="C4" t="n">
-        <v>71.64991095134071</v>
+        <v>68.9314515582813</v>
       </c>
       <c r="D4" t="n">
-        <v>63.71149901480101</v>
+        <v>51.30613502393831</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.38446955163304</v>
+        <v>26.21266370338984</v>
       </c>
       <c r="C5" t="n">
-        <v>113.1709666070511</v>
+        <v>85.38750657686634</v>
       </c>
       <c r="D5" t="n">
-        <v>42.77965621255477</v>
+        <v>38.85266539556753</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.60255641069606</v>
+        <v>19.40129813132547</v>
       </c>
       <c r="C6" t="n">
-        <v>111.5775900830585</v>
+        <v>75.39135145222532</v>
       </c>
       <c r="D6" t="n">
-        <v>34.45541742824607</v>
+        <v>34.13340418125311</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>75.69667498824607</v>
+        <v>45.27427712904591</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>32.54493639578176</v>
+        <v>24.70077223884975</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.251294613490274</v>
+        <v>7.283135191678808</v>
       </c>
       <c r="C21" t="n">
-        <v>75.2321816149616</v>
+        <v>75.56252761366764</v>
       </c>
       <c r="D21" t="n">
-        <v>5.438470960117706</v>
+        <v>6.372743292718957</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.415500263074653</v>
+        <v>4.876340846993907</v>
       </c>
       <c r="C2" t="n">
-        <v>6.531567476354029</v>
+        <v>5.335798772581414</v>
       </c>
       <c r="D2" t="n">
-        <v>29.35229286157114</v>
+        <v>28.14572493305181</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.34119053718816</v>
+        <v>22.65382827549515</v>
       </c>
       <c r="C3" t="n">
-        <v>28.28906009787184</v>
+        <v>18.40776945462769</v>
       </c>
       <c r="D3" t="n">
-        <v>78.75580083467912</v>
+        <v>65.06042036043613</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.67332436085984</v>
+        <v>38.33921134624644</v>
       </c>
       <c r="C4" t="n">
-        <v>66.00878864273855</v>
+        <v>67.39992513965628</v>
       </c>
       <c r="D4" t="n">
-        <v>83.53200341583987</v>
+        <v>68.62514627455629</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.17678100668922</v>
+        <v>35.14656781203582</v>
       </c>
       <c r="C5" t="n">
-        <v>123.7983855055228</v>
+        <v>109.415781638307</v>
       </c>
       <c r="D5" t="n">
-        <v>54.83060928218437</v>
+        <v>48.20381227851841</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.09565580013523</v>
+        <v>28.29691407950582</v>
       </c>
       <c r="C6" t="n">
-        <v>148.0053386491364</v>
+        <v>107.9146893985137</v>
       </c>
       <c r="D6" t="n">
-        <v>40.13090090649688</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="C7" t="n">
-        <v>120.0127663579471</v>
+        <v>80.6073770048886</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>68.26091787628073</v>
+        <v>44.2277340763188</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>32.50468473990763</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.44958649520605</v>
+        <v>7.492431850101938</v>
       </c>
       <c r="C21" t="n">
-        <v>83.80784807106807</v>
+        <v>85.22641229490955</v>
       </c>
       <c r="D21" t="n">
-        <v>6.518388183305293</v>
+        <v>7.492431850101938</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_76_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497642522887</v>
+        <v>10.84497634675192</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907226601399</v>
+        <v>37.78907199256285</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.769731257858504</v>
+        <v>4.375649517828034</v>
       </c>
       <c r="C2" t="n">
-        <v>14.63589477491145</v>
+        <v>7.646832868378405</v>
       </c>
       <c r="D2" t="n">
-        <v>25.73062558060465</v>
+        <v>25.47733467290897</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.38951715887451</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="C3" t="n">
-        <v>19.64968030049991</v>
+        <v>28.01907947920397</v>
       </c>
       <c r="D3" t="n">
-        <v>71.47614160768903</v>
+        <v>76.60577336237861</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.86622993697772</v>
+        <v>31.62602054460675</v>
       </c>
       <c r="C4" t="n">
-        <v>55.21152739143212</v>
+        <v>83.18740997164923</v>
       </c>
       <c r="D4" t="n">
-        <v>83.25122357242527</v>
+        <v>96.39682533229008</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.4612101034803</v>
+        <v>41.65064635267094</v>
       </c>
       <c r="C5" t="n">
-        <v>117.4170254279185</v>
+        <v>140.3408343220816</v>
       </c>
       <c r="D5" t="n">
-        <v>61.21196935978864</v>
+        <v>66.93064973702631</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.75605320992383</v>
+        <v>38.88309957439917</v>
       </c>
       <c r="C6" t="n">
-        <v>141.7663319886479</v>
+        <v>136.6141200367607</v>
       </c>
       <c r="D6" t="n">
-        <v>44.63908636439822</v>
+        <v>45.00135126726531</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>27.60772719112455</v>
       </c>
       <c r="C7" t="n">
-        <v>118.1562814492164</v>
+        <v>91.74628645727292</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>76.18853058807372</v>
+        <v>60.91744504851459</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>41.82343394861835</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
         <v>35.01894061048373</v>
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -954,7 +954,7 @@
         <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.687134782622017</v>
+        <v>7.689882265100149</v>
       </c>
       <c r="C21" t="n">
-        <v>94.1674010871197</v>
+        <v>94.20105774747682</v>
       </c>
       <c r="D21" t="n">
-        <v>8.648026630449769</v>
+        <v>8.651117548237668</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.276313073249859</v>
+        <v>5.292601873594555</v>
       </c>
       <c r="C2" t="n">
-        <v>16.19196488614264</v>
+        <v>14.00855799189774</v>
       </c>
       <c r="D2" t="n">
-        <v>29.47501132460199</v>
+        <v>21.59059551179585</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.20789383358884</v>
+        <v>14.7605767333508</v>
       </c>
       <c r="C3" t="n">
-        <v>38.70049450140927</v>
+        <v>28.7013941336555</v>
       </c>
       <c r="D3" t="n">
-        <v>74.44592841303563</v>
+        <v>78.36310175298041</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.49236398810894</v>
+        <v>29.86476516318797</v>
       </c>
       <c r="C4" t="n">
-        <v>52.07189823325082</v>
+        <v>75.78503228162829</v>
       </c>
       <c r="D4" t="n">
-        <v>97.45613110517236</v>
+        <v>110.2316139805361</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.96528864411543</v>
+        <v>44.17864669110647</v>
       </c>
       <c r="C5" t="n">
-        <v>108.6549271675158</v>
+        <v>146.452213781018</v>
       </c>
       <c r="D5" t="n">
-        <v>73.95014582239101</v>
+        <v>82.44226346412592</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.42903341341842</v>
+        <v>47.21519234034186</v>
       </c>
       <c r="C6" t="n">
-        <v>163.2607162254276</v>
+        <v>175.2557096759151</v>
       </c>
       <c r="D6" t="n">
-        <v>52.56866257159972</v>
+        <v>54.33973543006097</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.2551408965797</v>
+        <v>36.05173919535137</v>
       </c>
       <c r="C7" t="n">
-        <v>157.8012172421111</v>
+        <v>139.9550074743125</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04040019125691</v>
+        <v>42.39971985101125</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.69385894719101</v>
+        <v>21.36283004441059</v>
       </c>
       <c r="C8" t="n">
-        <v>114.2410716046801</v>
+        <v>89.70719647555229</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>65.78593191387449</v>
+        <v>55.91249525226433</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>38.29306920414684</v>
       </c>
       <c r="D10" t="n">
         <v>35.87306111317846</v>
@@ -1220,7 +1220,7 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
         <v>36.42774856607789</v>
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
         <v>35.58246379272139</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1265,7 +1265,7 @@
         <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.866423369533669</v>
+        <v>7.868307879512337</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2635038039377</v>
+        <v>102.2880024336604</v>
       </c>
       <c r="D21" t="n">
-        <v>9.833029211917086</v>
+        <v>9.835384849390422</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.431249284071608</v>
+        <v>6.552184178143213</v>
       </c>
       <c r="C2" t="n">
-        <v>15.87584212537517</v>
+        <v>9.317767461006477</v>
       </c>
       <c r="D2" t="n">
-        <v>40.81419730865264</v>
+        <v>33.99792299806704</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.68404147014855</v>
+        <v>15.96321767105314</v>
       </c>
       <c r="C3" t="n">
-        <v>49.57825906446393</v>
+        <v>40.36946559862884</v>
       </c>
       <c r="D3" t="n">
-        <v>78.43182409227768</v>
+        <v>76.89538893513142</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.15227837181205</v>
+        <v>28.37152690502857</v>
       </c>
       <c r="C4" t="n">
-        <v>71.45847014901258</v>
+        <v>72.97723384748241</v>
       </c>
       <c r="D4" t="n">
-        <v>107.3855273859246</v>
+        <v>119.280382570579</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.51154127830416</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="C5" t="n">
-        <v>102.7889846346411</v>
+        <v>143.0897278939727</v>
       </c>
       <c r="D5" t="n">
-        <v>88.03822537833273</v>
+        <v>98.56746950637979</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.20389439397641</v>
+        <v>52.20639766873265</v>
       </c>
       <c r="C6" t="n">
-        <v>166.2393387601124</v>
+        <v>198.158901868289</v>
       </c>
       <c r="D6" t="n">
-        <v>60.57874209054944</v>
+        <v>63.95988118397546</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.25620475974196</v>
+        <v>44.37597797966008</v>
       </c>
       <c r="C7" t="n">
-        <v>190.3795330598372</v>
+        <v>187.0258829021301</v>
       </c>
       <c r="D7" t="n">
-        <v>46.53189593818607</v>
+        <v>47.19064864773568</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.8704346652352</v>
+        <v>28.70630287217673</v>
       </c>
       <c r="C8" t="n">
-        <v>155.5481062608646</v>
+        <v>130.9307825768759</v>
       </c>
       <c r="D8" t="n">
         <v>39.97185777840888</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.19999879422586</v>
+        <v>15.19843620944487</v>
       </c>
       <c r="C9" t="n">
-        <v>97.07030425740334</v>
+        <v>78.87655580230145</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>55.51783267515713</v>
+        <v>49.96604940764142</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>37.6716229073586</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
         <v>36.23336252063703</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.029126403115406</v>
+        <v>8.030643262198073</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4004880428368</v>
+        <v>110.4213448552235</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04004880428368</v>
+        <v>11.04213448552235</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.625234418884976</v>
+        <v>5.955281573961152</v>
       </c>
       <c r="C2" t="n">
-        <v>10.92194320974577</v>
+        <v>6.409830761027425</v>
       </c>
       <c r="D2" t="n">
-        <v>33.40396563699773</v>
+        <v>27.93563092434299</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.58296251434013</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="C3" t="n">
-        <v>67.82894888641214</v>
+        <v>55.55710258332701</v>
       </c>
       <c r="D3" t="n">
-        <v>84.2143180702914</v>
+        <v>84.21922680881264</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.18910175848792</v>
+        <v>21.19887817780138</v>
       </c>
       <c r="C4" t="n">
-        <v>90.41110957949726</v>
+        <v>111.3547333541945</v>
       </c>
       <c r="D4" t="n">
-        <v>101.7316423571672</v>
+        <v>113.281904097631</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.79037332184348</v>
+        <v>29.40334374219198</v>
       </c>
       <c r="C5" t="n">
-        <v>99.32832397717107</v>
+        <v>118.3987731321654</v>
       </c>
       <c r="D5" t="n">
-        <v>59.86206626644928</v>
+        <v>64.69717370986481</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.45162930614931</v>
+        <v>27.53213261789756</v>
       </c>
       <c r="C6" t="n">
-        <v>125.3839080478814</v>
+        <v>123.1700669748049</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>31.07427833482005</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.78632315783946</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>109.3529497852352</v>
+        <v>92.0457195070682</v>
       </c>
       <c r="D7" t="n">
         <v>28.086820070797</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>71.5154115158589</v>
+        <v>58.0801941832413</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>42.3781214015178</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>28.96450251839364</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.469897297435728</v>
+        <v>3.62264902867073</v>
       </c>
       <c r="C2" t="n">
-        <v>5.088398351111218</v>
+        <v>3.548036203147973</v>
       </c>
       <c r="D2" t="n">
-        <v>24.39741219823749</v>
+        <v>19.70760341505047</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.02122290106171</v>
+        <v>20.41053477129119</v>
       </c>
       <c r="C3" t="n">
-        <v>56.13633372883262</v>
+        <v>40.80634332701868</v>
       </c>
       <c r="D3" t="n">
-        <v>91.43016369650546</v>
+        <v>87.71424863593127</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.46759931132452</v>
+        <v>28.1162725019244</v>
       </c>
       <c r="C4" t="n">
-        <v>131.5964075203552</v>
+        <v>128.5588801234156</v>
       </c>
       <c r="D4" t="n">
-        <v>116.4853468565883</v>
+        <v>126.133963293926</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.64373306101221</v>
+        <v>32.29949946972007</v>
       </c>
       <c r="C5" t="n">
-        <v>132.0696099138022</v>
+        <v>159.0676717805895</v>
       </c>
       <c r="D5" t="n">
-        <v>76.13453446434016</v>
+        <v>83.08039947188634</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.12711278440013</v>
+        <v>32.6440929139107</v>
       </c>
       <c r="C6" t="n">
-        <v>144.4229412763398</v>
+        <v>155.2103850506038</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>38.80259626265094</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>17.78632315783946</v>
       </c>
       <c r="C7" t="n">
-        <v>139.356141374722</v>
+        <v>124.204829055081</v>
       </c>
       <c r="D7" t="n">
         <v>30.96137734883166</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>94.29686699290613</v>
+        <v>77.52370746584938</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>47.59218345877262</v>
+        <v>42.82187136383736</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.16751900452771</v>
+        <v>3.384084336538756</v>
       </c>
       <c r="C2" t="n">
-        <v>13.03760951239764</v>
+        <v>2.955060589782899</v>
       </c>
       <c r="D2" t="n">
-        <v>22.21204180858409</v>
+        <v>16.25283324380595</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.80814259151115</v>
+        <v>16.34119053718816</v>
       </c>
       <c r="C3" t="n">
-        <v>37.3211389769425</v>
+        <v>26.42864819832414</v>
       </c>
       <c r="D3" t="n">
-        <v>89.43721585688444</v>
+        <v>83.29147522829939</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.78514578815274</v>
+        <v>33.38727592602553</v>
       </c>
       <c r="C4" t="n">
-        <v>135.744291570798</v>
+        <v>116.1152279720873</v>
       </c>
       <c r="D4" t="n">
-        <v>132.7195268940135</v>
+        <v>138.9222088894449</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.08047192068179</v>
+        <v>36.88916998707391</v>
       </c>
       <c r="C5" t="n">
-        <v>185.0594422505238</v>
+        <v>196.3740845419683</v>
       </c>
       <c r="D5" t="n">
-        <v>96.53034302006766</v>
+        <v>105.0470043544087</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.21140421824511</v>
+        <v>37.63529824230149</v>
       </c>
       <c r="C6" t="n">
-        <v>176.3022527286422</v>
+        <v>201.8620542087079</v>
       </c>
       <c r="D6" t="n">
-        <v>49.67054334866313</v>
+        <v>52.28690098048088</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.63146906247572</v>
+        <v>26.17044855210722</v>
       </c>
       <c r="C7" t="n">
-        <v>172.4734366820796</v>
+        <v>169.1197865243725</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07548106670254</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>134.268724771315</v>
+        <v>116.5776311407875</v>
       </c>
       <c r="D8" t="n">
         <v>29.45733986592554</v>
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>76.21405602838412</v>
+        <v>66.00780689503428</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.62030998483051</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>42.70602513473626</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
         <v>30.32127784566274</v>
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.46605242207675</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.509347132054847</v>
+        <v>2.035162990903638</v>
       </c>
       <c r="C2" t="n">
-        <v>6.304783756673016</v>
+        <v>1.411753198706913</v>
       </c>
       <c r="D2" t="n">
-        <v>15.50375974546563</v>
+        <v>11.35391219961436</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.2681813541754</v>
+        <v>15.89940407027709</v>
       </c>
       <c r="C3" t="n">
-        <v>44.860961345558</v>
+        <v>21.58863201638736</v>
       </c>
       <c r="D3" t="n">
-        <v>89.6777440444249</v>
+        <v>81.21017009529616</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.57567367424968</v>
+        <v>36.87149852839745</v>
       </c>
       <c r="C4" t="n">
-        <v>134.9912910816407</v>
+        <v>110.4868683836403</v>
       </c>
       <c r="D4" t="n">
-        <v>144.1549241530804</v>
+        <v>148.596350767093</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.08676331753477</v>
+        <v>38.99992755120455</v>
       </c>
       <c r="C5" t="n">
-        <v>228.0354480039279</v>
+        <v>231.3243028131548</v>
       </c>
       <c r="D5" t="n">
-        <v>102.34719816773</v>
+        <v>110.9620342724958</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.87931145230244</v>
+        <v>31.19503330244241</v>
       </c>
       <c r="C6" t="n">
-        <v>210.9589284362589</v>
+        <v>238.1690478071635</v>
       </c>
       <c r="D6" t="n">
-        <v>48.90576188705487</v>
+        <v>51.24035792775378</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.845145904636261</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>177.6236851385584</v>
+        <v>167.5627346654371</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>95.63204387068178</v>
+        <v>84.03269474500573</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
         <v>31.8390597964283</v>
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.209333245182823</v>
+        <v>3.261365873507904</v>
       </c>
       <c r="C2" t="n">
-        <v>5.790347959647687</v>
+        <v>3.572579895754143</v>
       </c>
       <c r="D2" t="n">
-        <v>11.87816547368216</v>
+        <v>10.54691558672348</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.72130682518092</v>
+        <v>11.51590057081509</v>
       </c>
       <c r="C3" t="n">
-        <v>34.92567457858028</v>
+        <v>13.39103868592649</v>
       </c>
       <c r="D3" t="n">
-        <v>82.23609644623407</v>
+        <v>73.20401756716342</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.67853619901734</v>
+        <v>34.15303913533804</v>
       </c>
       <c r="C4" t="n">
-        <v>123.9004872667645</v>
+        <v>83.67239333754716</v>
       </c>
       <c r="D4" t="n">
-        <v>153.433421705917</v>
+        <v>153.675913388866</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.53608497091033</v>
+        <v>45.99487994396307</v>
       </c>
       <c r="C5" t="n">
-        <v>239.1046533693107</v>
+        <v>220.402359603409</v>
       </c>
       <c r="D5" t="n">
-        <v>124.4119778206771</v>
+        <v>132.756833306775</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.2642386678252</v>
+        <v>39.64788103600744</v>
       </c>
       <c r="C6" t="n">
-        <v>276.8911407580662</v>
+        <v>296.6144521363846</v>
       </c>
       <c r="D6" t="n">
-        <v>64.72466264558373</v>
+        <v>68.10580173900973</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.18745705824891</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C7" t="n">
-        <v>233.0786859606437</v>
+        <v>243.9780489731918</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32743037379547</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>149.5398103108741</v>
+        <v>138.357703959503</v>
       </c>
       <c r="D8" t="n">
         <v>33.12907627980861</v>
@@ -3058,7 +3058,7 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>62.23593221531803</v>
+        <v>56.68905768632355</v>
       </c>
       <c r="D9" t="n">
         <v>32.61562223048752</v>
@@ -3072,7 +3072,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>24.91184799526281</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
         <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.46681318560274</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.291399141712055</v>
+        <v>2.072469403665017</v>
       </c>
       <c r="C2" t="n">
-        <v>3.183807804872406</v>
+        <v>2.805834938737384</v>
       </c>
       <c r="D2" t="n">
-        <v>8.814130888727863</v>
+        <v>7.576147033672636</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.26341148437441</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C3" t="n">
-        <v>30.07584091960103</v>
+        <v>13.73955912093411</v>
       </c>
       <c r="D3" t="n">
-        <v>75.33441008537899</v>
+        <v>67.46570223584081</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.85422798034851</v>
+        <v>30.3497485290859</v>
       </c>
       <c r="C4" t="n">
-        <v>112.1715474441278</v>
+        <v>64.63041486597602</v>
       </c>
       <c r="D4" t="n">
-        <v>157.7727465586879</v>
+        <v>155.0415244454733</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.51845456996289</v>
+        <v>49.70097752749479</v>
       </c>
       <c r="C5" t="n">
-        <v>240.7245370813179</v>
+        <v>203.1481437012713</v>
       </c>
       <c r="D5" t="n">
-        <v>141.0280577150543</v>
+        <v>147.1639808665969</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.1875234781737</v>
+        <v>45.8466360406218</v>
       </c>
       <c r="C6" t="n">
-        <v>321.8522403694574</v>
+        <v>328.4535119328129</v>
       </c>
       <c r="D6" t="n">
-        <v>75.91462297858888</v>
+        <v>82.19388129495147</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.21119892960008</v>
+        <v>15.51063197939536</v>
       </c>
       <c r="C7" t="n">
-        <v>289.2523261022378</v>
+        <v>306.9787626501181</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>44.01665831990574</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>189.4282195344221</v>
+        <v>182.1681952615169</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>68.78124415953151</v>
+        <v>65.00936947981526</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>10.75504610002381</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.116468123906875</v>
+        <v>3.826852551154067</v>
       </c>
       <c r="C2" t="n">
-        <v>4.411974182885166</v>
+        <v>6.998879383575511</v>
       </c>
       <c r="D2" t="n">
-        <v>15.38889526406875</v>
+        <v>11.10553003043992</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.66178006812036</v>
+        <v>9.311876974780997</v>
       </c>
       <c r="C3" t="n">
-        <v>22.09423208407447</v>
+        <v>12.32093368829747</v>
       </c>
       <c r="D3" t="n">
-        <v>67.13190801639689</v>
+        <v>59.59699438630262</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.91956310817654</v>
+        <v>26.17633903833271</v>
       </c>
       <c r="C4" t="n">
-        <v>96.12880820903068</v>
+        <v>51.06364334098934</v>
       </c>
       <c r="D4" t="n">
-        <v>158.0918145625681</v>
+        <v>153.2547436237441</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.88031856220246</v>
+        <v>48.08109381548755</v>
       </c>
       <c r="C5" t="n">
-        <v>226.0964962880405</v>
+        <v>167.1180029554133</v>
       </c>
       <c r="D5" t="n">
-        <v>155.6315548157257</v>
+        <v>162.9701189049705</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.77370897306707</v>
+        <v>53.81646390369741</v>
       </c>
       <c r="C6" t="n">
-        <v>345.8824789263066</v>
+        <v>327.4874721918341</v>
       </c>
       <c r="D6" t="n">
-        <v>94.30962971306137</v>
+        <v>100.9914045881652</v>
       </c>
     </row>
     <row r="7">
@@ -3652,10 +3652,10 @@
         <v>28.38625312059227</v>
       </c>
       <c r="C7" t="n">
-        <v>356.0258962065845</v>
+        <v>377.5251891818854</v>
       </c>
       <c r="D7" t="n">
-        <v>50.36463897556562</v>
+        <v>52.76010337392783</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>262.3622564829176</v>
+        <v>266.2843385613836</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>125.0265518835355</v>
+        <v>122.8078020719377</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>47.11898106532567</v>
+        <v>46.6919208139783</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.640721397974672</v>
+        <v>4.877322594698154</v>
       </c>
       <c r="C2" t="n">
-        <v>6.899722865446583</v>
+        <v>6.283185307179586</v>
       </c>
       <c r="D2" t="n">
-        <v>7.834346679889546</v>
+        <v>5.961172060186633</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.00709321810798</v>
+        <v>2.763619787454771</v>
       </c>
       <c r="C2" t="n">
-        <v>2.611448893296516</v>
+        <v>4.031056073637403</v>
       </c>
       <c r="D2" t="n">
-        <v>11.4491417269263</v>
+        <v>8.263370426645404</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.74585051778709</v>
+        <v>12.72345024703866</v>
       </c>
       <c r="C3" t="n">
-        <v>24.45533531278805</v>
+        <v>18.48140053244621</v>
       </c>
       <c r="D3" t="n">
-        <v>73.42491080061895</v>
+        <v>64.27993093555992</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.32492709903924</v>
+        <v>36.46309148343079</v>
       </c>
       <c r="C4" t="n">
-        <v>135.2720709250553</v>
+        <v>79.62661104834605</v>
       </c>
       <c r="D4" t="n">
-        <v>159.0490185742088</v>
+        <v>157.1601359912379</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.21390749300135</v>
+        <v>31.19503330244241</v>
       </c>
       <c r="C5" t="n">
-        <v>310.5513425458723</v>
+        <v>265.9799967730672</v>
       </c>
       <c r="D5" t="n">
-        <v>140.7826207889926</v>
+        <v>147.5075925630833</v>
       </c>
     </row>
     <row r="6">
@@ -4260,10 +4260,10 @@
         <v>17.5899736169901</v>
       </c>
       <c r="C6" t="n">
-        <v>295.4874057719093</v>
+        <v>309.6157369837251</v>
       </c>
       <c r="D6" t="n">
-        <v>74.46556336712058</v>
+        <v>79.69827863075608</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>184.5106452838498</v>
+        <v>187.2654293419663</v>
       </c>
       <c r="D7" t="n">
-        <v>31.73990327829938</v>
+        <v>32.45854259780804</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>92.12720456652069</v>
+        <v>90.45823346930109</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.817836895366598</v>
+        <v>6.804493338134643</v>
       </c>
       <c r="C2" t="n">
-        <v>6.282203559475339</v>
+        <v>4.182245220091412</v>
       </c>
       <c r="D2" t="n">
-        <v>18.09164669386022</v>
+        <v>15.92100251977052</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.86165568915921</v>
+        <v>10.36725575684632</v>
       </c>
       <c r="C3" t="n">
-        <v>17.38675184221101</v>
+        <v>16.08102739556275</v>
       </c>
       <c r="D3" t="n">
-        <v>9.714393533522189</v>
+        <v>8.143597206727291</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39867628738219</v>
+        <v>13.39906389353611</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14601115158909</v>
+        <v>70.14804038380672</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576314857339081</v>
+        <v>1.576360458063072</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.297109701488289</v>
+        <v>4.279438242811846</v>
       </c>
       <c r="C2" t="n">
-        <v>7.961973881441631</v>
+        <v>3.039490892348125</v>
       </c>
       <c r="D2" t="n">
-        <v>17.64691498383642</v>
+        <v>20.84643075197677</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.98285262513807</v>
+        <v>18.2065111752571</v>
       </c>
       <c r="C3" t="n">
-        <v>21.83406894244906</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D3" t="n">
-        <v>22.5605622435917</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.56302446061893</v>
+        <v>12.13734686760332</v>
       </c>
       <c r="C4" t="n">
-        <v>27.01867856857647</v>
+        <v>25.04045694451915</v>
       </c>
       <c r="D4" t="n">
-        <v>20.16509784522949</v>
+        <v>19.33552103514093</v>
       </c>
     </row>
     <row r="5">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44219851624283</v>
+        <v>15.44371260840356</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15121277482841</v>
+        <v>86.15965981530408</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250989161314279</v>
+        <v>3.251307917558645</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.603414985213294</v>
+        <v>4.702571503342222</v>
       </c>
       <c r="C2" t="n">
-        <v>7.598727230870312</v>
+        <v>10.69810473317749</v>
       </c>
       <c r="D2" t="n">
-        <v>16.80850244440964</v>
+        <v>23.34301516387641</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.36435157146258</v>
+        <v>16.29701189049705</v>
       </c>
       <c r="C3" t="n">
-        <v>27.38094347144354</v>
+        <v>13.62174939642449</v>
       </c>
       <c r="D3" t="n">
-        <v>31.4404702285041</v>
+        <v>31.6859071545658</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.46238747316702</v>
+        <v>25.12979598560561</v>
       </c>
       <c r="C4" t="n">
-        <v>43.30390948662256</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D4" t="n">
-        <v>26.94210224764522</v>
+        <v>24.78520254141498</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.60287520586555</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C5" t="n">
-        <v>30.75324683553134</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D5" t="n">
-        <v>29.69786805346602</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73697069604042</v>
+        <v>16.74052418386336</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0955212458466</v>
+        <v>102.1171975215665</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021091208812125</v>
+        <v>5.022157255159007</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.413757751844412</v>
+        <v>5.492878405260903</v>
       </c>
       <c r="C2" t="n">
-        <v>9.325621442640452</v>
+        <v>13.95259837275567</v>
       </c>
       <c r="D2" t="n">
-        <v>17.50554331442488</v>
+        <v>30.5932219597391</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.59015354343935</v>
+        <v>16.19883712007237</v>
       </c>
       <c r="C3" t="n">
-        <v>28.58358440914589</v>
+        <v>30.14456325889832</v>
       </c>
       <c r="D3" t="n">
-        <v>37.21805546799658</v>
+        <v>42.37713965381357</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.52093248252334</v>
+        <v>28.52467954689108</v>
       </c>
       <c r="C4" t="n">
-        <v>56.9727827728509</v>
+        <v>33.92331017254428</v>
       </c>
       <c r="D4" t="n">
-        <v>36.11849803924015</v>
+        <v>34.29342905704534</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.0402359603409</v>
+        <v>24.66641106920112</v>
       </c>
       <c r="C5" t="n">
-        <v>57.82493978013714</v>
+        <v>47.90928796724435</v>
       </c>
       <c r="D5" t="n">
-        <v>32.32404316232624</v>
+        <v>31.83316931020283</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.22392059202629</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>31.47679489356124</v>
+        <v>29.7057220351</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
         <v>39.46527596301753</v>
@@ -5546,7 +5546,7 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
         <v>46.86470840992573</v>
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06473401811307</v>
+        <v>18.07094535009325</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8508838324519</v>
+        <v>117.8914053791798</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881803435471645</v>
+        <v>6.884169657178381</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.810784734987623</v>
+        <v>5.412375093512666</v>
       </c>
       <c r="C2" t="n">
-        <v>6.13101441302133</v>
+        <v>8.915250902265285</v>
       </c>
       <c r="D2" t="n">
-        <v>32.63525718457247</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.0824100538945</v>
+        <v>15.73250696055514</v>
       </c>
       <c r="C3" t="n">
-        <v>30.96923133046564</v>
+        <v>41.27758222505715</v>
       </c>
       <c r="D3" t="n">
-        <v>39.74605580643212</v>
+        <v>52.87202261221197</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.66284393128262</v>
+        <v>21.77320058478576</v>
       </c>
       <c r="C4" t="n">
-        <v>54.06288257746336</v>
+        <v>47.60494617892783</v>
       </c>
       <c r="D4" t="n">
-        <v>40.18980576875168</v>
+        <v>40.8151790563569</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.99681807717579</v>
+        <v>20.7148765596077</v>
       </c>
       <c r="C5" t="n">
-        <v>62.26734814185396</v>
+        <v>41.65064635267094</v>
       </c>
       <c r="D5" t="n">
-        <v>30.31146036862028</v>
+        <v>30.06602344255857</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.06920536538279</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="C6" t="n">
-        <v>42.7070068824405</v>
+        <v>36.38749691020379</v>
       </c>
       <c r="D6" t="n">
-        <v>30.99377502307181</v>
+        <v>30.83276839957533</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>20.84054026575129</v>
       </c>
       <c r="D7" t="n">
         <v>30.72183090899544</v>
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5916,7 +5916,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061011466902607</v>
+        <v>7.063849028741361</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19698250221194</v>
+        <v>66.22358464445026</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295758600176955</v>
+        <v>5.29788677155602</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.373506095970292</v>
+        <v>4.505240214788612</v>
       </c>
       <c r="C2" t="n">
-        <v>3.388993075059989</v>
+        <v>7.096072406295946</v>
       </c>
       <c r="D2" t="n">
-        <v>26.07816426790802</v>
+        <v>28.31360379047801</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.39504779220149</v>
+        <v>17.76963344686727</v>
       </c>
       <c r="C3" t="n">
-        <v>26.44828315240908</v>
+        <v>37.12478943609314</v>
       </c>
       <c r="D3" t="n">
-        <v>57.55495916146926</v>
+        <v>68.19710427550469</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.67783218875358</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="C4" t="n">
-        <v>68.9314515582813</v>
+        <v>82.72795204606172</v>
       </c>
       <c r="D4" t="n">
-        <v>51.30613502393831</v>
+        <v>58.65746183333842</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.21266370338984</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="C5" t="n">
-        <v>85.38750657686634</v>
+        <v>69.5813685384927</v>
       </c>
       <c r="D5" t="n">
-        <v>38.85266539556753</v>
+        <v>38.90175278077987</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.40129813132547</v>
+        <v>21.49438423677967</v>
       </c>
       <c r="C6" t="n">
-        <v>75.39135145222532</v>
+        <v>54.29948377418685</v>
       </c>
       <c r="D6" t="n">
-        <v>34.13340418125311</v>
+        <v>33.61013265488955</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.881290643244144</v>
+        <v>10.59992996275281</v>
       </c>
       <c r="C7" t="n">
-        <v>45.27427712904591</v>
+        <v>39.70482240285375</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>24.70077223884975</v>
+        <v>24.28352946454485</v>
       </c>
       <c r="D8" t="n">
         <v>32.3780392860598</v>
@@ -6168,7 +6168,7 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
         <v>31.17343485294896</v>
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.283135191678808</v>
+        <v>7.286519992022646</v>
       </c>
       <c r="C21" t="n">
-        <v>75.56252761366764</v>
+        <v>75.59764491723496</v>
       </c>
       <c r="D21" t="n">
-        <v>6.372743292718957</v>
+        <v>6.375704993019816</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.876340846993907</v>
+        <v>4.079161711145497</v>
       </c>
       <c r="C2" t="n">
-        <v>5.335798772581414</v>
+        <v>6.56200165518568</v>
       </c>
       <c r="D2" t="n">
-        <v>28.14572493305181</v>
+        <v>24.37188675792707</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.65382827549515</v>
+        <v>16.54735755507999</v>
       </c>
       <c r="C3" t="n">
-        <v>18.40776945462769</v>
+        <v>31.35702167364312</v>
       </c>
       <c r="D3" t="n">
-        <v>65.06042036043613</v>
+        <v>75.02515955854125</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.33921134624644</v>
+        <v>31.72812230584842</v>
       </c>
       <c r="C4" t="n">
-        <v>67.39992513965628</v>
+        <v>88.81576956009619</v>
       </c>
       <c r="D4" t="n">
-        <v>68.62514627455629</v>
+        <v>79.65213648865647</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.14656781203582</v>
+        <v>35.04839304161113</v>
       </c>
       <c r="C5" t="n">
-        <v>109.415781638307</v>
+        <v>117.0979574240383</v>
       </c>
       <c r="D5" t="n">
-        <v>48.20381227851841</v>
+        <v>50.80544369477245</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.29691407950582</v>
+        <v>30.47050349670826</v>
       </c>
       <c r="C6" t="n">
-        <v>107.9146893985137</v>
+        <v>85.25300714138454</v>
       </c>
       <c r="D6" t="n">
-        <v>39.04410619789565</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="C7" t="n">
-        <v>80.6073770048886</v>
+        <v>60.6052492785641</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>44.2277340763188</v>
+        <v>40.05530633326986</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>28.06718511671205</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6507,7 +6507,7 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.492431850101938</v>
+        <v>7.495672890637558</v>
       </c>
       <c r="C21" t="n">
-        <v>85.22641229490955</v>
+        <v>85.26327913100224</v>
       </c>
       <c r="D21" t="n">
-        <v>7.492431850101938</v>
+        <v>7.495672890637558</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_76_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634675192</v>
+        <v>10.84497627626798</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907199256285</v>
+        <v>37.78907174696319</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.375649517828034</v>
+        <v>1.328304643845934</v>
       </c>
       <c r="C2" t="n">
-        <v>7.646832868378405</v>
+        <v>2.799944452511903</v>
       </c>
       <c r="D2" t="n">
-        <v>25.47733467290897</v>
+        <v>16.35493500504761</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.09437095279471</v>
+        <v>13.08178815908875</v>
       </c>
       <c r="C3" t="n">
-        <v>28.01907947920397</v>
+        <v>32.40749171718721</v>
       </c>
       <c r="D3" t="n">
-        <v>76.60577336237861</v>
+        <v>62.22807823368407</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.62602054460675</v>
+        <v>25.20637230653686</v>
       </c>
       <c r="C4" t="n">
-        <v>83.18740997164923</v>
+        <v>117.9147715139716</v>
       </c>
       <c r="D4" t="n">
-        <v>96.39682533229008</v>
+        <v>74.25350586300326</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.65064635267094</v>
+        <v>24.96093538047516</v>
       </c>
       <c r="C5" t="n">
-        <v>140.3408343220816</v>
+        <v>136.8556299720054</v>
       </c>
       <c r="D5" t="n">
-        <v>66.93064973702631</v>
+        <v>48.42470551197393</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.88309957439917</v>
+        <v>16.46292725251477</v>
       </c>
       <c r="C6" t="n">
-        <v>136.6141200367607</v>
+        <v>78.20896736341366</v>
       </c>
       <c r="D6" t="n">
-        <v>45.00135126726531</v>
+        <v>30.26924521733767</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.60772719112455</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>91.74628645727292</v>
+        <v>42.16017341117502</v>
       </c>
       <c r="D7" t="n">
-        <v>39.1059563032632</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>60.91744504851459</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.689882265100149</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.20105774747682</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.651117548237668</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.292601873594555</v>
+        <v>1.853539665617978</v>
       </c>
       <c r="C2" t="n">
-        <v>14.00855799189774</v>
+        <v>5.12177777305561</v>
       </c>
       <c r="D2" t="n">
-        <v>21.59059551179585</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.7605767333508</v>
+        <v>8.62465358180823</v>
       </c>
       <c r="C3" t="n">
-        <v>28.7013941336555</v>
+        <v>20.07183181332604</v>
       </c>
       <c r="D3" t="n">
-        <v>78.36310175298041</v>
+        <v>60.81436153956867</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.86476516318797</v>
+        <v>25.2701859073129</v>
       </c>
       <c r="C4" t="n">
-        <v>75.78503228162829</v>
+        <v>97.36679206408591</v>
       </c>
       <c r="D4" t="n">
-        <v>110.2316139805361</v>
+        <v>87.96066730969723</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.17864669110647</v>
+        <v>31.80862561759666</v>
       </c>
       <c r="C5" t="n">
-        <v>146.452213781018</v>
+        <v>181.917849596934</v>
       </c>
       <c r="D5" t="n">
-        <v>82.44226346412592</v>
+        <v>63.24909584610077</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.21519234034186</v>
+        <v>24.47300677146449</v>
       </c>
       <c r="C6" t="n">
-        <v>175.2557096759151</v>
+        <v>149.7361598517235</v>
       </c>
       <c r="D6" t="n">
-        <v>54.33973543006097</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.05173919535137</v>
+        <v>12.27675504160636</v>
       </c>
       <c r="C7" t="n">
-        <v>139.9550074743125</v>
+        <v>77.43338667705868</v>
       </c>
       <c r="D7" t="n">
-        <v>42.39971985101125</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.36283004441059</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>89.70719647555229</v>
+        <v>42.47531442423825</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>55.91249525226433</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>38.29306920414684</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.868307879512337</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2880024336604</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.835384849390422</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.552184178143213</v>
+        <v>1.001382658331747</v>
       </c>
       <c r="C2" t="n">
-        <v>9.317767461006477</v>
+        <v>2.226603793231766</v>
       </c>
       <c r="D2" t="n">
-        <v>33.99792299806704</v>
+        <v>14.17938209243668</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96321767105314</v>
+        <v>8.46757394912874</v>
       </c>
       <c r="C3" t="n">
-        <v>40.36946559862884</v>
+        <v>21.38246499849553</v>
       </c>
       <c r="D3" t="n">
-        <v>76.89538893513142</v>
+        <v>64.40264939859075</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.37152690502857</v>
+        <v>27.41432289338793</v>
       </c>
       <c r="C4" t="n">
-        <v>72.97723384748241</v>
+        <v>87.7692265073691</v>
       </c>
       <c r="D4" t="n">
-        <v>119.280382570579</v>
+        <v>96.90733413849841</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.12955930589413</v>
+        <v>31.857713002809</v>
       </c>
       <c r="C5" t="n">
-        <v>143.0897278939727</v>
+        <v>206.5842606661351</v>
       </c>
       <c r="D5" t="n">
-        <v>98.56746950637979</v>
+        <v>70.85764055401356</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.20639766873265</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="C6" t="n">
-        <v>198.158901868289</v>
+        <v>188.1764912115074</v>
       </c>
       <c r="D6" t="n">
-        <v>63.95988118397546</v>
+        <v>38.52083467153211</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.37597797966008</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>187.0258829021301</v>
+        <v>74.01984990939251</v>
       </c>
       <c r="D7" t="n">
-        <v>47.19064864773568</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.70630287217673</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>130.9307825768759</v>
+        <v>40.05530633326986</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.19843620944487</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>78.87655580230145</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.6716229073586</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.030643262198073</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4213448552235</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04213448552235</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.955281573961152</v>
+        <v>1.265472790774139</v>
       </c>
       <c r="C2" t="n">
-        <v>6.409830761027425</v>
+        <v>6.635632733004192</v>
       </c>
       <c r="D2" t="n">
-        <v>27.93563092434299</v>
+        <v>12.01561015227671</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3600647277471</v>
+        <v>5.910121179565799</v>
       </c>
       <c r="C3" t="n">
-        <v>55.55710258332701</v>
+        <v>14.33842522052466</v>
       </c>
       <c r="D3" t="n">
-        <v>84.21922680881264</v>
+        <v>60.90271883295088</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.19887817780138</v>
+        <v>22.30923483130452</v>
       </c>
       <c r="C4" t="n">
-        <v>111.3547333541945</v>
+        <v>70.10562181256049</v>
       </c>
       <c r="D4" t="n">
-        <v>113.281904097631</v>
+        <v>106.1475435308694</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.40334374219198</v>
+        <v>36.64373306101221</v>
       </c>
       <c r="C5" t="n">
-        <v>118.3987731321654</v>
+        <v>185.7466656434966</v>
       </c>
       <c r="D5" t="n">
-        <v>64.69717370986481</v>
+        <v>87.54735152620933</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.53213261789756</v>
+        <v>28.82018560586937</v>
       </c>
       <c r="C6" t="n">
-        <v>123.1700669748049</v>
+        <v>259.3816704528243</v>
       </c>
       <c r="D6" t="n">
-        <v>31.07427833482005</v>
+        <v>50.31456984264904</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>92.0457195070682</v>
+        <v>164.20908450773</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>58.0801941832413</v>
+        <v>65.50711556586842</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.09685853201771</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.20280516861837</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.58823110575986</v>
-      </c>
-      <c r="D14" t="n">
-        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.62264902867073</v>
+        <v>0.7873616588059419</v>
       </c>
       <c r="C2" t="n">
-        <v>3.548036203147973</v>
+        <v>3.398810552102457</v>
       </c>
       <c r="D2" t="n">
-        <v>19.70760341505047</v>
+        <v>8.539241531538757</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.41053477129119</v>
+        <v>5.296528864411542</v>
       </c>
       <c r="C3" t="n">
-        <v>40.80634332701868</v>
+        <v>20.56270566544944</v>
       </c>
       <c r="D3" t="n">
-        <v>87.71424863593127</v>
+        <v>57.86420968830701</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.1162725019244</v>
+        <v>18.50594422505237</v>
       </c>
       <c r="C4" t="n">
-        <v>128.5588801234156</v>
+        <v>55.84966339919255</v>
       </c>
       <c r="D4" t="n">
-        <v>126.133963293926</v>
+        <v>111.4440723952809</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.29949946972007</v>
+        <v>37.94454876913922</v>
       </c>
       <c r="C5" t="n">
-        <v>159.0676717805895</v>
+        <v>168.4679060487527</v>
       </c>
       <c r="D5" t="n">
-        <v>83.08039947188634</v>
+        <v>101.0954698448153</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.6440929139107</v>
+        <v>34.77743067523902</v>
       </c>
       <c r="C6" t="n">
-        <v>155.2103850506038</v>
+        <v>285.7465050503724</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80259626265094</v>
+        <v>59.61270234957058</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.78632315783946</v>
+        <v>11.67788894201581</v>
       </c>
       <c r="C7" t="n">
-        <v>124.204829055081</v>
+        <v>238.4085942469997</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>77.52370746584938</v>
+        <v>104.1437964665016</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>42.82187136383736</v>
+        <v>46.37187106239383</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.384084336538756</v>
+        <v>1.463785827031994</v>
       </c>
       <c r="C2" t="n">
-        <v>2.955060589782899</v>
+        <v>7.766606088296517</v>
       </c>
       <c r="D2" t="n">
-        <v>16.25283324380595</v>
+        <v>9.254935607934682</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.34119053718816</v>
+        <v>3.995713156284519</v>
       </c>
       <c r="C3" t="n">
-        <v>26.42864819832414</v>
+        <v>16.86151682043897</v>
       </c>
       <c r="D3" t="n">
-        <v>83.29147522829939</v>
+        <v>51.9099098620501</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.38727592602553</v>
+        <v>14.62607729786898</v>
       </c>
       <c r="C4" t="n">
-        <v>116.1152279720873</v>
+        <v>53.56513649141022</v>
       </c>
       <c r="D4" t="n">
-        <v>138.9222088894449</v>
+        <v>114.4177861914445</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.88916998707391</v>
+        <v>33.99301425954582</v>
       </c>
       <c r="C5" t="n">
-        <v>196.3740845419683</v>
+        <v>137.3955912093411</v>
       </c>
       <c r="D5" t="n">
-        <v>105.0470043544087</v>
+        <v>115.4044426342126</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.63529824230149</v>
+        <v>41.94222542083224</v>
       </c>
       <c r="C6" t="n">
-        <v>201.8620542087079</v>
+        <v>281.7615911188346</v>
       </c>
       <c r="D6" t="n">
-        <v>52.28690098048088</v>
+        <v>74.1032984642535</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.17044855210722</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="C7" t="n">
-        <v>169.1197865243725</v>
+        <v>315.1233416045496</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>46.23246288839079</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>116.5776311407875</v>
+        <v>194.5185813809418</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>41.64082887562846</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>66.00780689503428</v>
+        <v>80.09686819868024</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>41.56719779780995</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.035162990903638</v>
+        <v>0.9945104244020189</v>
       </c>
       <c r="C2" t="n">
-        <v>1.411753198706913</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="D2" t="n">
-        <v>11.35391219961436</v>
+        <v>6.737734494245859</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.89940407027709</v>
+        <v>5.910121179565799</v>
       </c>
       <c r="C3" t="n">
-        <v>21.58863201638736</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D3" t="n">
-        <v>81.21017009529616</v>
+        <v>55.27730448761665</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.87149852839745</v>
+        <v>23.57274412667016</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4868683836403</v>
+        <v>76.93367709559706</v>
       </c>
       <c r="D4" t="n">
-        <v>148.596350767093</v>
+        <v>117.5957035100914</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.99992755120455</v>
+        <v>25.50089661781091</v>
       </c>
       <c r="C5" t="n">
-        <v>231.3243028131548</v>
+        <v>222.9058162492383</v>
       </c>
       <c r="D5" t="n">
-        <v>110.9620342724958</v>
+        <v>106.9859560702962</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.19503330244241</v>
+        <v>14.28933783531233</v>
       </c>
       <c r="C6" t="n">
-        <v>238.1690478071635</v>
+        <v>273.8320149116332</v>
       </c>
       <c r="D6" t="n">
-        <v>51.24035792775378</v>
+        <v>63.1950997223672</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.26435217434965</v>
+        <v>4.671155576806323</v>
       </c>
       <c r="C7" t="n">
-        <v>167.5627346654371</v>
+        <v>136.7810171464826</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>84.03269474500573</v>
+        <v>58.99812828671206</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.261365873507904</v>
+        <v>0.5262167694762904</v>
       </c>
       <c r="C2" t="n">
-        <v>3.572579895754143</v>
+        <v>2.355212742488098</v>
       </c>
       <c r="D2" t="n">
-        <v>10.54691558672348</v>
+        <v>5.684319207589032</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.51590057081509</v>
+        <v>4.687845287778519</v>
       </c>
       <c r="C3" t="n">
-        <v>13.39103868592649</v>
+        <v>19.82148614874311</v>
       </c>
       <c r="D3" t="n">
-        <v>73.20401756716342</v>
+        <v>48.20381227851839</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.15303913533804</v>
+        <v>16.4511462800638</v>
       </c>
       <c r="C4" t="n">
-        <v>83.67239333754716</v>
+        <v>65.37065263497811</v>
       </c>
       <c r="D4" t="n">
-        <v>153.675913388866</v>
+        <v>113.652022982132</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.99487994396307</v>
+        <v>23.97918767622835</v>
       </c>
       <c r="C5" t="n">
-        <v>220.402359603409</v>
+        <v>166.6516727958961</v>
       </c>
       <c r="D5" t="n">
-        <v>132.756833306775</v>
+        <v>111.8210635137117</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.64788103600744</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="C6" t="n">
-        <v>296.6144521363846</v>
+        <v>259.5024254204467</v>
       </c>
       <c r="D6" t="n">
-        <v>68.10580173900973</v>
+        <v>66.45548384817086</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>243.9780489731918</v>
+        <v>179.360396827371</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>138.357703959503</v>
+        <v>69.67954330891736</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>56.68905768632355</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>17.93653055658923</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.072469403665017</v>
+        <v>0.4771293842639499</v>
       </c>
       <c r="C2" t="n">
-        <v>2.805834938737384</v>
+        <v>6.456954650831271</v>
       </c>
       <c r="D2" t="n">
-        <v>7.576147033672636</v>
+        <v>11.51099183229385</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.43245201595411</v>
+        <v>3.126866438026091</v>
       </c>
       <c r="C3" t="n">
-        <v>13.73955912093411</v>
+        <v>13.45485228670254</v>
       </c>
       <c r="D3" t="n">
-        <v>67.46570223584081</v>
+        <v>42.02861921880595</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.3497485290859</v>
+        <v>12.58404207303562</v>
       </c>
       <c r="C4" t="n">
-        <v>64.63041486597602</v>
+        <v>56.93449461238528</v>
       </c>
       <c r="D4" t="n">
-        <v>155.0415244454733</v>
+        <v>111.2271061526424</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.70097752749479</v>
+        <v>24.96093538047516</v>
       </c>
       <c r="C5" t="n">
-        <v>203.1481437012713</v>
+        <v>141.5680189523901</v>
       </c>
       <c r="D5" t="n">
-        <v>147.1639808665969</v>
+        <v>127.8726384781471</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.8466360406218</v>
+        <v>23.30570875111504</v>
       </c>
       <c r="C6" t="n">
-        <v>328.4535119328129</v>
+        <v>266.1842002955505</v>
       </c>
       <c r="D6" t="n">
-        <v>82.19388129495147</v>
+        <v>85.73602701187396</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.51063197939536</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>306.9787626501181</v>
+        <v>280.5687676581747</v>
       </c>
       <c r="D7" t="n">
-        <v>44.01665831990574</v>
+        <v>44.73529763941441</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>182.1681952615169</v>
+        <v>155.0474149316988</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>65.00936947981526</v>
+        <v>57.57655761096267</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>22.40937309713768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.826852551154067</v>
+        <v>0.3907355862902305</v>
       </c>
       <c r="C2" t="n">
-        <v>6.998879383575511</v>
+        <v>11.62978330450772</v>
       </c>
       <c r="D2" t="n">
-        <v>11.10553003043992</v>
+        <v>13.22217808079604</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.311876974780997</v>
+        <v>2.32674205906494</v>
       </c>
       <c r="C3" t="n">
-        <v>12.32093368829747</v>
+        <v>19.75767254796706</v>
       </c>
       <c r="D3" t="n">
-        <v>59.59699438630262</v>
+        <v>41.37084825696059</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.17633903833271</v>
+        <v>9.265734832681398</v>
       </c>
       <c r="C4" t="n">
-        <v>51.06364334098934</v>
+        <v>44.58018150214342</v>
       </c>
       <c r="D4" t="n">
-        <v>153.2547436237441</v>
+        <v>107.5003918673215</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.08109381548755</v>
+        <v>22.48202242725196</v>
       </c>
       <c r="C5" t="n">
-        <v>167.1180029554133</v>
+        <v>122.9148125717007</v>
       </c>
       <c r="D5" t="n">
-        <v>162.9701189049705</v>
+        <v>136.7819988941869</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.81646390369741</v>
+        <v>28.2566624236317</v>
       </c>
       <c r="C6" t="n">
-        <v>327.4874721918341</v>
+        <v>247.4671803140851</v>
       </c>
       <c r="D6" t="n">
-        <v>100.9914045881652</v>
+        <v>104.7750602403324</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.38625312059227</v>
+        <v>18.38518925743002</v>
       </c>
       <c r="C7" t="n">
-        <v>377.5251891818854</v>
+        <v>333.6283040818979</v>
       </c>
       <c r="D7" t="n">
-        <v>52.76010337392783</v>
+        <v>57.25159912085699</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>266.2843385613836</v>
+        <v>258.9408657336174</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>122.8078020719377</v>
+        <v>120.1453022980204</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>24.73906039931537</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6919208139783</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.877322594698154</v>
+        <v>8.005170780428491</v>
       </c>
       <c r="C2" t="n">
-        <v>6.283185307179586</v>
+        <v>10.08942115654447</v>
       </c>
       <c r="D2" t="n">
-        <v>5.961172060186633</v>
+        <v>15.93180174451724</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.763619787454771</v>
+        <v>1.242892593576462</v>
       </c>
       <c r="C2" t="n">
-        <v>4.031056073637403</v>
+        <v>18.48925451408018</v>
       </c>
       <c r="D2" t="n">
-        <v>8.263370426645404</v>
+        <v>13.18094467721768</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.72345024703866</v>
+        <v>1.811324514335365</v>
       </c>
       <c r="C3" t="n">
-        <v>18.48140053244621</v>
+        <v>32.19150722225291</v>
       </c>
       <c r="D3" t="n">
-        <v>64.27993093555992</v>
+        <v>41.82245220091412</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.46309148343079</v>
+        <v>6.955682484588651</v>
       </c>
       <c r="C4" t="n">
-        <v>79.62661104834605</v>
+        <v>46.77536936883928</v>
       </c>
       <c r="D4" t="n">
-        <v>157.1601359912379</v>
+        <v>103.1993551750162</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.19503330244241</v>
+        <v>18.84955592153876</v>
       </c>
       <c r="C5" t="n">
-        <v>265.9799967730672</v>
+        <v>102.7398972494287</v>
       </c>
       <c r="D5" t="n">
-        <v>147.5075925630833</v>
+        <v>143.3597085126405</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.5899736169901</v>
+        <v>29.54471541160352</v>
       </c>
       <c r="C6" t="n">
-        <v>309.6157369837251</v>
+        <v>225.2885179274453</v>
       </c>
       <c r="D6" t="n">
-        <v>79.69827863075608</v>
+        <v>119.5474179461341</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="C7" t="n">
-        <v>187.2654293419663</v>
+        <v>348.0010904720711</v>
       </c>
       <c r="D7" t="n">
-        <v>32.45854259780804</v>
+        <v>71.14529263135785</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="C8" t="n">
-        <v>90.45823346930109</v>
+        <v>338.9680298452962</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>35.61093447614454</v>
+        <v>207.896857346713</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>85.83911052081987</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.804493338134643</v>
+        <v>6.854562471051231</v>
       </c>
       <c r="C2" t="n">
-        <v>4.182245220091412</v>
+        <v>8.705156893556467</v>
       </c>
       <c r="D2" t="n">
-        <v>15.92100251977052</v>
+        <v>20.65989868816988</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.36725575684632</v>
+        <v>12.89034735676062</v>
       </c>
       <c r="C3" t="n">
-        <v>16.08102739556275</v>
+        <v>19.91966091916778</v>
       </c>
       <c r="D3" t="n">
-        <v>8.143597206727291</v>
+        <v>13.85736884544373</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39906389353611</v>
+        <v>11.67688274804877</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14804038380672</v>
+        <v>59.94133143998366</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576360458063072</v>
+        <v>0.7784588498699176</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.279438242811846</v>
+        <v>3.685480881742526</v>
       </c>
       <c r="C2" t="n">
-        <v>3.039490892348125</v>
+        <v>7.936448441131216</v>
       </c>
       <c r="D2" t="n">
-        <v>20.84643075197677</v>
+        <v>19.52008960353933</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2065111752571</v>
+        <v>19.85584731839174</v>
       </c>
       <c r="C3" t="n">
-        <v>16.3902779224005</v>
+        <v>29.16772429317274</v>
       </c>
       <c r="D3" t="n">
-        <v>19.54659679155399</v>
+        <v>28.55413197801848</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.13734686760332</v>
+        <v>15.78748483199296</v>
       </c>
       <c r="C4" t="n">
-        <v>25.04045694451915</v>
+        <v>32.4428346345401</v>
       </c>
       <c r="D4" t="n">
-        <v>19.33552103514093</v>
+        <v>21.59452250261284</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44371260840356</v>
+        <v>13.62488490685211</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15965981530408</v>
+        <v>73.73467126061139</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251307917558645</v>
+        <v>1.602927636100248</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.702571503342222</v>
+        <v>2.940334374219197</v>
       </c>
       <c r="C2" t="n">
-        <v>10.69810473317749</v>
+        <v>10.26908098642164</v>
       </c>
       <c r="D2" t="n">
-        <v>23.34301516387641</v>
+        <v>20.15626211589126</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.29701189049705</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C3" t="n">
-        <v>13.62174939642449</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D3" t="n">
-        <v>31.6859071545658</v>
+        <v>38.04763227808514</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.12979598560561</v>
+        <v>29.15005283449629</v>
       </c>
       <c r="C4" t="n">
-        <v>34.47210713921825</v>
+        <v>57.5853933403009</v>
       </c>
       <c r="D4" t="n">
-        <v>24.78520254141498</v>
+        <v>31.5494442236755</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.06920536538279</v>
+        <v>14.1126232485479</v>
       </c>
       <c r="C5" t="n">
-        <v>28.61794557879453</v>
+        <v>37.99363615435157</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>27.70982895236623</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74052418386336</v>
+        <v>14.83040360977547</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1171975215665</v>
+        <v>87.33459903534441</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022157255159007</v>
+        <v>2.471733934962578</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.492878405260903</v>
+        <v>3.863177216211199</v>
       </c>
       <c r="C2" t="n">
-        <v>13.95259837275567</v>
+        <v>7.212900383101315</v>
       </c>
       <c r="D2" t="n">
-        <v>30.5932219597391</v>
+        <v>15.27010379185489</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.19883712007237</v>
+        <v>12.63018421513522</v>
       </c>
       <c r="C3" t="n">
-        <v>30.14456325889832</v>
+        <v>36.45720099720531</v>
       </c>
       <c r="D3" t="n">
-        <v>42.37713965381357</v>
+        <v>45.34201772063894</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.52467954689108</v>
+        <v>30.31146036862027</v>
       </c>
       <c r="C4" t="n">
-        <v>33.92331017254428</v>
+        <v>67.65517954276044</v>
       </c>
       <c r="D4" t="n">
-        <v>34.29342905704534</v>
+        <v>43.52087572926111</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.66641106920112</v>
+        <v>29.59969328304134</v>
       </c>
       <c r="C5" t="n">
-        <v>47.90928796724435</v>
+        <v>76.99356370555611</v>
       </c>
       <c r="D5" t="n">
-        <v>31.83316931020283</v>
+        <v>32.59402378099411</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.465430527271</v>
+        <v>11.95474179461341</v>
       </c>
       <c r="C6" t="n">
-        <v>29.7057220351</v>
+        <v>37.75605320992383</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>33.93214590188251</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07094535009325</v>
+        <v>16.06470016862133</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8914053791798</v>
+        <v>100.615753687681</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884169657178381</v>
+        <v>3.382042140762386</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.412375093512666</v>
+        <v>2.965859814529614</v>
       </c>
       <c r="C2" t="n">
-        <v>8.915250902265285</v>
+        <v>8.379216655746527</v>
       </c>
       <c r="D2" t="n">
-        <v>33.45305302221006</v>
+        <v>19.14898897133403</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.73250696055514</v>
+        <v>12.91489104936679</v>
       </c>
       <c r="C3" t="n">
-        <v>41.27758222505715</v>
+        <v>31.61718481526853</v>
       </c>
       <c r="D3" t="n">
-        <v>52.87202261221197</v>
+        <v>46.85881792370026</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.77320058478576</v>
+        <v>27.32498385230147</v>
       </c>
       <c r="C4" t="n">
-        <v>47.60494617892783</v>
+        <v>80.57105233983148</v>
       </c>
       <c r="D4" t="n">
-        <v>40.8151790563569</v>
+        <v>55.76032435810609</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.7148765596077</v>
+        <v>37.42913122440965</v>
       </c>
       <c r="C5" t="n">
-        <v>41.65064635267094</v>
+        <v>101.6599747747572</v>
       </c>
       <c r="D5" t="n">
-        <v>30.06602344255857</v>
+        <v>40.42346172236243</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.11574841810989</v>
+        <v>25.80131141531043</v>
       </c>
       <c r="C6" t="n">
-        <v>36.38749691020379</v>
+        <v>81.50960314509145</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>36.30699359845555</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>20.84054026575129</v>
+        <v>36.47094546506476</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.063849028741361</v>
+        <v>17.32195993078063</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22358464445026</v>
+        <v>114.3249355431522</v>
       </c>
       <c r="D21" t="n">
-        <v>5.29788677155602</v>
+        <v>4.330489982695157</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.505240214788612</v>
+        <v>2.701769682087222</v>
       </c>
       <c r="C2" t="n">
-        <v>7.096072406295946</v>
+        <v>7.379797492823274</v>
       </c>
       <c r="D2" t="n">
-        <v>28.31360379047801</v>
+        <v>29.71455776443821</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.76963344686727</v>
+        <v>11.36863841517807</v>
       </c>
       <c r="C3" t="n">
-        <v>37.12478943609314</v>
+        <v>31.96570525027615</v>
       </c>
       <c r="D3" t="n">
-        <v>68.19710427550469</v>
+        <v>50.35383975081891</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.55471281509523</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="C4" t="n">
-        <v>82.72795204606172</v>
+        <v>78.91189871965437</v>
       </c>
       <c r="D4" t="n">
-        <v>58.65746183333842</v>
+        <v>64.3113468620958</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.75891633757857</v>
+        <v>39.09810232162923</v>
       </c>
       <c r="C5" t="n">
-        <v>69.5813685384927</v>
+        <v>125.0992012136498</v>
       </c>
       <c r="D5" t="n">
-        <v>38.90175278077987</v>
+        <v>50.09367660919352</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.49438423677967</v>
+        <v>37.43403996293088</v>
       </c>
       <c r="C6" t="n">
-        <v>54.29948377418685</v>
+        <v>119.9499345048753</v>
       </c>
       <c r="D6" t="n">
-        <v>33.61013265488955</v>
+        <v>40.05039759474864</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.59992996275281</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>39.70482240285375</v>
+        <v>74.31928295918779</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>24.28352946454485</v>
+        <v>36.38356991938679</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286519992022646</v>
+        <v>17.70915682694669</v>
       </c>
       <c r="C21" t="n">
-        <v>75.59764491723496</v>
+        <v>126.6204713126689</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375704993019816</v>
+        <v>5.312747048084008</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.079161711145497</v>
+        <v>2.54861704022472</v>
       </c>
       <c r="C2" t="n">
-        <v>6.56200165518568</v>
+        <v>4.663301595172349</v>
       </c>
       <c r="D2" t="n">
-        <v>24.37188675792707</v>
+        <v>23.48929557180918</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.54735755507999</v>
+        <v>16.27737693641212</v>
       </c>
       <c r="C3" t="n">
-        <v>31.35702167364312</v>
+        <v>47.66385104118265</v>
       </c>
       <c r="D3" t="n">
-        <v>75.02515955854125</v>
+        <v>56.87264450701772</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.72812230584842</v>
+        <v>18.77396134831176</v>
       </c>
       <c r="C4" t="n">
-        <v>88.81576956009619</v>
+        <v>110.1678003797601</v>
       </c>
       <c r="D4" t="n">
-        <v>79.65213648865647</v>
+        <v>60.712259778327</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.04839304161113</v>
+        <v>21.08303194870026</v>
       </c>
       <c r="C5" t="n">
-        <v>117.0979574240383</v>
+        <v>71.66758241001718</v>
       </c>
       <c r="D5" t="n">
-        <v>50.80544369477245</v>
+        <v>38.33724785083795</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.47050349670826</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>85.25300714138454</v>
+        <v>48.94601354292898</v>
       </c>
       <c r="D6" t="n">
-        <v>38.64158963915446</v>
+        <v>25.96231803880691</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.56484908730718</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>60.6052492785641</v>
+        <v>25.57158245251667</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>26.82920126165683</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>40.05530633326986</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.73437264497238</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.495672890637558</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.26327913100224</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.495672890637558</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
